--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>23785.4</v>
+        <v>23881.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>25.27</v>
+        <v>25.38</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.1136363636363636</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>941.2504946576969</v>
+        <v>940.9456264775414</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.2620605182648434</v>
+        <v>0.2615092176974554</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03957261574990107</v>
+        <v>0.03940110323089047</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>91.66666666666666</v>
+        <v>88.63636363636364</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>94.16666666666666</v>
+        <v>92.04545454545455</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>28.27571428571429</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>26614.53005822828</v>
+        <v>26605.9096926714</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.1189439764825597</v>
+        <v>0.114094337498593</v>
       </c>
     </row>
     <row r="14">
@@ -736,10 +736,10 @@
         <v>33.64428571428572</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31667.70057097631</v>
+        <v>31657.44349881797</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.3313923907513143</v>
+        <v>0.3256219745581448</v>
       </c>
     </row>
     <row r="15"/>
@@ -4207,7 +4207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4298,6 +4298,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>23881.2</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.113636363636</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.261509217697</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>23881.2</v>
+        <v>23790.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>25.38</v>
+        <v>25.28</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.1136363636363636</v>
+        <v>0.09848484848484848</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>940.9456264775414</v>
+        <v>941.0878164556962</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.2615092176974554</v>
+        <v>0.2618194901278241</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03940110323089047</v>
+        <v>0.03955696202531645</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>88.63636363636364</v>
+        <v>90.15151515151516</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>92.04545454545455</v>
+        <v>93.10606060606059</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>28.27571428571429</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>26605.9096926714</v>
+        <v>26609.93021586799</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.114094337498593</v>
+        <v>0.1185013562386981</v>
       </c>
     </row>
     <row r="14">
@@ -736,10 +736,10 @@
         <v>33.64428571428572</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31657.44349881797</v>
+        <v>31662.22737906871</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.3256219745581448</v>
+        <v>0.3308657323688968</v>
       </c>
     </row>
     <row r="15"/>
@@ -4207,7 +4207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4331,6 +4331,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>23790.7</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.09848484848480001</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.261819490128</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>23790.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>25.28</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.09848484848484848</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>941.0878164556962</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.2618194901278241</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>90.15151515151516</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>100</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>93.10606060606059</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>28.27571428571429</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>26609.93021586799</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>0.1185013562386981</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>33.64428571428572</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>31662.22737906871</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.3308657323688968</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,19 +811,19 @@
       <c r="B18" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.218855498309952</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.1463701118425471</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.1825776644607492</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="30" t="n">
         <v>0.1208770170571605</v>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -821,19 +836,19 @@
       <c r="B19" t="n">
         <v>8</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.1243344997343012</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.15245932820649</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.1785081032571778</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="30" t="n">
         <v>0.1171198842073442</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -846,17 +861,17 @@
       <c r="B20" t="n">
         <v>9</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.111652889184817</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.1419265398225793</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.1463009130875816</v>
       </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n">
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -869,19 +884,19 @@
       <c r="B21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>0.07269742099130849</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.1711200220152822</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.1182425537751224</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="30" t="n">
         <v>0.1313046060711542</v>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -894,21 +909,20 @@
       <c r="B22" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>0.05080328048427174</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.1273194898895045</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1118414665109817</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1044,16 +1058,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>13745.82</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>29.73</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1063,16 +1077,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>14713.05</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>27.14</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1082,16 +1096,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>15169.2</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>29.27</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1101,16 +1115,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>15594.26</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>28.98</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1120,16 +1134,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>16313.93</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>28.3</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1139,16 +1153,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>16467.75</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>26.43</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1158,16 +1172,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>16015.22</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>25.06</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1177,16 +1191,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>15680.57</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>25.19</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1196,16 +1210,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>16022.97</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>25.82</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1215,16 +1229,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>15655.42</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>25.28</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1234,16 +1248,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>14998.39</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>24.05</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1253,16 +1267,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>15243.32</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>26.43</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1272,16 +1286,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>15516.07</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>26.77</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1291,16 +1305,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>15247.96</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>27.13</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1310,16 +1324,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>14458.17</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>25.28</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1329,16 +1343,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>15680.63</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>27.31</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1348,16 +1362,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>16120.08</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>28.68</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1367,16 +1381,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>15715.37</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>27.74</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1386,16 +1400,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>16105.74</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>28.76</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1405,16 +1419,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>16635.52</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>29.58</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1424,16 +1438,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>16004.77</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>28.42</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1443,16 +1457,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>15789.56</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>27.68</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1462,16 +1476,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>15431.88</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>27.78</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1481,16 +1495,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>15567.29</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>28.47</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1500,16 +1514,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>16180.39</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>29.32</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1519,16 +1533,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>16853.79</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>29.01</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1538,16 +1552,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>17622.42</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>28.57</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1557,16 +1571,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>18363.11</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>29.33</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1576,16 +1590,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>18074.74</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>26.44</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1595,16 +1609,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>18396.83</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>25.62</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1614,16 +1628,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>18137.11</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>24.71</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1633,16 +1647,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>19425.73</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>23.84</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1652,16 +1666,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>20885.12</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>26.68</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1671,16 +1685,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>21319.36</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>26.4</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1690,16 +1704,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>21844.81</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>26.8</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1709,16 +1723,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>21963.09</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>30.87</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1728,16 +1742,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>22262.48</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>30.27</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1747,16 +1761,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>22093.62</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>29.78</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1766,16 +1780,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>23710.09</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>31.75</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1785,16 +1799,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>25190.86</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>33.28</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1804,16 +1818,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>25625.86</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>33.79</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1823,16 +1837,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>26377.43</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>38.32</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1842,16 +1856,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>24347.06</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>35.1</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1861,16 +1875,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>24008.85</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>34.95</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1880,16 +1894,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>23621.15</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>34.51</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1899,16 +1913,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>23796.4</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>34.53</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1918,16 +1932,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>22217.3</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>31.93</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1937,16 +1951,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>23559.75</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>33.24</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1956,16 +1970,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>24615.7</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>34.52</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1975,16 +1989,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>24694.15</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>33.98</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1994,16 +2008,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>25380.55</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>35.03</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2013,16 +2027,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>24797.1</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>33.81</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2032,16 +2046,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>24793</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>33.24</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2051,16 +2065,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>24555.3</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>32.22</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2070,16 +2084,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>25391.45</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>33.09</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2089,16 +2103,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>25678</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>32.92</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2108,16 +2122,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>25703.45</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>31.56</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2127,16 +2141,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>24904.9</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>30.51</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2146,16 +2160,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>25153.25</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>30.42</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2165,16 +2179,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>22582</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>27.63</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2184,16 +2198,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>24173.95</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>29.38</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2203,16 +2217,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>24083.4</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>28.13</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2222,16 +2236,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>24151.5</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>26.26</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2241,16 +2255,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>25081.25</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>26.96</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2260,16 +2274,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>24651.4</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>26.19</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2371,13 +2385,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>42369</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>7485.07</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>24.71</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2385,12 +2399,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2398,31 +2412,31 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="30">
         <f>IFERROR((B42/B2)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>42460</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>7214.11</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>22.52</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2430,12 +2444,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2443,31 +2457,31 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="30">
         <f>IFERROR((B43/B3)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>42551</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>7978.96</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>24.24</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2475,12 +2489,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2488,31 +2502,31 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="30">
         <f>IFERROR((B44/B4)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>42643</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>8320.34</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>24.63</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2520,12 +2534,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2533,28 +2547,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>42735</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>7758.3</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>21.73</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2562,15 +2576,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2578,28 +2592,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>42825</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>8717.110000000001</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>24.31</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2607,15 +2621,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2623,28 +2637,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>42916</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>8971.02</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>25.3</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2652,15 +2666,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2668,28 +2682,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>9249.33</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>27.48</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2697,15 +2711,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2713,28 +2727,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>10102.21</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>30.1</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2742,15 +2756,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2758,28 +2772,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>9544.389999999999</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>27.05</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2787,15 +2801,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2803,28 +2817,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>9768.07</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>27.22</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2832,15 +2846,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2848,28 +2862,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>9832.809999999999</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>26.24</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2877,15 +2891,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2893,28 +2907,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>10049.5</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>24.44</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2922,15 +2936,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2938,28 +2952,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>10236.82</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>24.62</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2967,15 +2981,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2983,28 +2997,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>10264.32</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>24</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3012,15 +3026,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3028,28 +3042,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>10209.42</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>22.65</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3057,15 +3071,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3073,28 +3087,28 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>10558.46</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>22.94</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3102,15 +3116,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3118,28 +3132,28 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="30">
         <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="16" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>8703.58</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>19.21</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3147,15 +3161,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3163,28 +3177,28 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="30">
         <f>IFERROR((B39/B19)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L19" s="16" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>10255.97</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>23.57</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3192,15 +3206,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3208,28 +3222,28 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="30">
         <f>IFERROR((B40/B20)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L20" s="16" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>11278.19</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>26.71</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3237,15 +3251,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3253,28 +3267,28 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="30">
         <f>IFERROR((B41/B21)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L21" s="16" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>13088.08</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>30.56</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3282,15 +3296,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3298,28 +3312,28 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="30">
         <f>IFERROR((B42/B22)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L22" s="16" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>13673.8</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>29.81</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3327,15 +3341,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3343,28 +3357,28 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="30">
         <f>IFERROR((B43/B23)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L23" s="16" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>15169.2</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>29.27</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3372,15 +3386,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3388,28 +3402,28 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="30">
         <f>IFERROR((B44/B24)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L24" s="16" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>16467.75</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>26.43</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3417,15 +3431,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3433,25 +3447,25 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>16022.97</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>25.82</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3459,15 +3473,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3475,25 +3489,25 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="30">
         <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>15243.32</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>26.43</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3501,15 +3515,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3517,25 +3531,25 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="30">
         <f>IFERROR((B39/B27)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>14458.17</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>25.28</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3543,15 +3557,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3559,25 +3573,25 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="30">
         <f>IFERROR((B40/B28)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>15715.37</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>27.74</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3585,15 +3599,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3601,25 +3615,25 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="30">
         <f>IFERROR((B41/B29)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>16004.77</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>28.42</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3627,15 +3641,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3643,25 +3657,25 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="30">
         <f>IFERROR((B42/B30)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>15567.29</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>28.47</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3669,15 +3683,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3685,25 +3699,25 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="30">
         <f>IFERROR((B43/B31)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>17622.42</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>28.57</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3711,15 +3725,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3727,25 +3741,25 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="30">
         <f>IFERROR((B44/B32)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>18396.83</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>25.62</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3753,15 +3767,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3769,22 +3783,22 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>20885.12</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>26.68</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3792,15 +3806,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3808,22 +3822,22 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="30">
         <f>IFERROR(B38/B34-1,"")</f>
         <v/>
       </c>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>21963.09</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>30.87</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3831,15 +3845,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3847,22 +3861,22 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="30">
         <f>IFERROR(B39/B35-1,"")</f>
         <v/>
       </c>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>23710.09</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>31.75</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3870,15 +3884,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3886,22 +3900,22 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="30">
         <f>IFERROR(B40/B36-1,"")</f>
         <v/>
       </c>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>26377.43</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>38.32</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3909,15 +3923,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3925,22 +3939,22 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="30">
         <f>IFERROR(B41/B37-1,"")</f>
         <v/>
       </c>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>23621.15</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>34.51</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3948,15 +3962,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="33">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="30">
         <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="30">
         <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3964,22 +3978,22 @@
         <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="30">
         <f>IFERROR(B42/B38-1,"")</f>
         <v/>
       </c>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="16" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>23559.75</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>33.24</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3987,15 +4001,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="33">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="30">
         <f>IF(AND(D39=D35,E35&lt;&gt;""),E39/E35-1,"")</f>
         <v/>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="30">
         <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4003,22 +4017,22 @@
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="30">
         <f>IFERROR(B43/B39-1,"")</f>
         <v/>
       </c>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="16" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>25380.55</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>35.03</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4026,15 +4040,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="33">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="30">
         <f>IF(AND(D40=D36,E36&lt;&gt;""),E40/E36-1,"")</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="30">
         <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4042,22 +4056,22 @@
         <f>IF(G40="","",IF(G40&lt;=20%,"Q1 Cheapest",IF(G40&lt;=40%,"Q2",IF(G40&lt;=60%,"Q3",IF(G40&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="30">
         <f>IFERROR(B44/B40-1,"")</f>
         <v/>
       </c>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n"/>
+      <c r="J40" s="30" t="n"/>
+      <c r="K40" s="30" t="n"/>
+      <c r="L40" s="30" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>24555.3</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>32.22</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4065,15 +4079,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="33">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="30">
         <f>IF(AND(D41=D37,E37&lt;&gt;""),E41/E37-1,"")</f>
         <v/>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="30">
         <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4081,19 +4095,19 @@
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="16" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="30" t="n"/>
+      <c r="L41" s="30" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>25703.45</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>31.56</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4101,15 +4115,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="33">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="30">
         <f>IF(AND(D42=D38,E38&lt;&gt;""),E42/E38-1,"")</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="30">
         <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4117,19 +4131,19 @@
         <f>IF(G42="","",IF(G42&lt;=20%,"Q1 Cheapest",IF(G42&lt;=40%,"Q2",IF(G42&lt;=60%,"Q3",IF(G42&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n"/>
+      <c r="I42" s="30" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>22582</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>27.63</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4137,15 +4151,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="33">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="30">
         <f>IF(AND(D43=D39,E39&lt;&gt;""),E43/E39-1,"")</f>
         <v/>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="30">
         <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4153,19 +4167,19 @@
         <f>IF(G43="","",IF(G43&lt;=20%,"Q1 Cheapest",IF(G43&lt;=40%,"Q2",IF(G43&lt;=60%,"Q3",IF(G43&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="16" t="n"/>
+      <c r="I43" s="30" t="n"/>
+      <c r="J43" s="30" t="n"/>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>24151.5</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>26.26</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4173,15 +4187,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="33">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="30">
         <f>IF(AND(D44=D40,E40&lt;&gt;""),E44/E40-1,"")</f>
         <v/>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="30">
         <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4189,10 +4203,10 @@
         <f>IF(G44="","",IF(G44&lt;=20%,"Q1 Cheapest",IF(G44&lt;=40%,"Q2",IF(G44&lt;=60%,"Q3",IF(G44&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I44" s="16" t="n"/>
-      <c r="J44" s="16" t="n"/>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="16" t="n"/>
+      <c r="I44" s="30" t="n"/>
+      <c r="J44" s="30" t="n"/>
+      <c r="K44" s="30" t="n"/>
+      <c r="L44" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4269,30 +4283,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>23785.4</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>25.27</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.08333333333329999</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.262060518265</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -4302,30 +4316,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>23881.2</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>25.38</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.113636363636</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.261509217697</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -4335,30 +4349,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>23790.7</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>25.28</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.09848484848480001</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.261819490128</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4478,4 +4492,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty Low Volatility 50 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4391,6 +4394,1112 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY Low Volatility 50 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Asian Paints Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Avenue Supermarts Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Axis Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bajaj Auto Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bajaj Finserv Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bharti Airtel Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Britannia Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cipla Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Colgate Palmolive (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dabur India Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Divi's Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Godrej Consumer Products Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Grasim Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HCL Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HDFC Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HDFC Life Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Hero MotoCorp Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ICICI Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Infosys Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ITC Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>JSW Steel Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kotak Mahindra Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Larsen &amp; Toubro Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lupin Ltd.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Marico Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Maruti Suzuki India Ltd.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MRF Ltd.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MRF</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Nestle India Ltd.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NTPC Ltd.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Page Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Textiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pidilite Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Power Grid Corporation of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Reliance Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SBI Cards and Payment Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SBI Life Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>State Bank of India</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tata Consumer Products Ltd.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Tech Mahindra Ltd.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Titan Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Torrent Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>UltraTech Cement Ltd.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>United Spirits Ltd.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Wipro Ltd.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -4492,43 +5601,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty Low Volatility 50 Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23790.7</v>
+        <v>23934.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.28</v>
+        <v>25.43</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.09848484848484848</v>
+        <v>0.1136363636363636</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>941.0878164556962</v>
+        <v>941.2033031852143</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2618194901278241</v>
+        <v>0.2618662173744675</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03955696202531645</v>
+        <v>0.03932363350373574</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>90.15151515151516</v>
+        <v>88.63636363636364</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.10606060606059</v>
+        <v>92.04545454545455</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>28.27571428571429</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>26609.93021586799</v>
+        <v>26613.19568563564</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1185013562386981</v>
+        <v>0.1119038256277738</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.64428571428572</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31662.22737906871</v>
+        <v>31666.11284759283</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3308657323688968</v>
+        <v>0.3230155609235437</v>
       </c>
     </row>
     <row r="16">
@@ -4224,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4381,6 +4381,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>23934.8</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.113636363636</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.261866217374</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23934.8</v>
+        <v>23635.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.43</v>
+        <v>25.11</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1136363636363636</v>
+        <v>0.06818181818181818</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>941.2033031852143</v>
+        <v>941.2604540023895</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2618662173744675</v>
+        <v>0.2619627922989656</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03932363350373574</v>
+        <v>0.03982477100756671</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>88.63636363636364</v>
+        <v>93.18181818181819</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>92.04545454545455</v>
+        <v>95.22727272727273</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>28.27571428571429</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>26613.19568563564</v>
+        <v>26614.81166581328</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1119038256277738</v>
+        <v>0.1260738465039541</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.64428571428572</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31666.11284759283</v>
+        <v>31668.03564601468</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3230155609235437</v>
+        <v>0.3398759742845765</v>
       </c>
     </row>
     <row r="16">
@@ -4224,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4414,6 +4414,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>23635.05</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.0681818181818</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.261962792299</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4454,7 +4487,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23635.05</v>
+        <v>23702.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.11</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.07575757575757576</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>941.2604540023895</v>
+        <v>940.9547439460104</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2619627922989656</v>
+        <v>0.261576038546077</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03982477100756671</v>
+        <v>0.03969829297340214</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>93.18181818181819</v>
+        <v>92.42424242424242</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>95.22727272727273</v>
+        <v>94.69696969696969</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>28.27571428571429</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>26614.81166581328</v>
+        <v>26606.16749560483</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1260738465039541</v>
+        <v>0.1224975897464982</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.64428571428572</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31668.03564601468</v>
+        <v>31657.75024953213</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3398759742845765</v>
+        <v>0.3356207111665626</v>
       </c>
     </row>
     <row r="16">
@@ -4224,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4447,6 +4447,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>23702.65</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.0757575757576</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.261576038546</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4487,7 +4520,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23702.65</v>
+        <v>23439.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.19</v>
+        <v>24.91</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.07575757575757576</v>
+        <v>0.05303030303030303</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>940.9547439460104</v>
+        <v>940.9574468085107</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.261576038546077</v>
+        <v>0.2614441856440681</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03969829297340214</v>
+        <v>0.04014452027298274</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>92.42424242424242</v>
+        <v>94.6969696969697</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>94.69696969696969</v>
+        <v>96.28787878787878</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>28.27571428571429</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>26606.16749560483</v>
+        <v>26606.24392097265</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1224975897464982</v>
+        <v>0.1351149853759248</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.64428571428572</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31657.75024953213</v>
+        <v>31657.84118541034</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3356207111665626</v>
+        <v>0.3506337099271664</v>
       </c>
     </row>
     <row r="16">
@@ -4224,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4480,6 +4480,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>23439.25</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>24.91</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.0530303030303</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.261444185644</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4520,7 +4553,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23439.25</v>
+        <v>23213.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>24.91</v>
+        <v>24.67</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05303030303030303</v>
+        <v>0.03787878787878788</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>940.9574468085107</v>
+        <v>940.9708147547628</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2614441856440681</v>
+        <v>0.2616826522583751</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04014452027298274</v>
+        <v>0.04053506282934739</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.6969696969697</v>
+        <v>96.21212121212122</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>96.28787878787878</v>
+        <v>97.34848484848484</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>28.27571428571429</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>26606.24392097265</v>
+        <v>26606.62190920146</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1351149853759248</v>
+        <v>0.146157855116104</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.64428571428572</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31657.84118541034</v>
+        <v>31658.29094041346</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3506337099271664</v>
+        <v>0.3637732352770862</v>
       </c>
     </row>
     <row r="16">
@@ -4224,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4513,6 +4513,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>23213.75</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.0378787878788</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.261682652258</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4553,7 +4586,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4803,17 +4836,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Colgate Palmolive (India) Ltd.</t>
+          <t>Coal India Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -4823,17 +4856,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dabur India Ltd.</t>
+          <t>Divi's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4876,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Ltd.</t>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4863,17 +4896,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd.</t>
+          <t>Godrej Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -4883,17 +4916,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Godrej Consumer Products Ltd.</t>
+          <t>Grasim Industries Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -4903,17 +4936,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd.</t>
+          <t>Havells India Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5063,17 +5096,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
+          <t>ITC Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5083,17 +5116,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infosys Ltd.</t>
+          <t>JSW Steel Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -5103,17 +5136,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ITC Ltd.</t>
+          <t>Kotak Mahindra Bank Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5123,17 +5156,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JSW Steel Ltd.</t>
+          <t>Larsen &amp; Toubro Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -5143,17 +5176,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Ltd.</t>
+          <t>Lupin Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5163,17 +5196,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd.</t>
+          <t>Marico Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5183,17 +5216,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lupin Ltd.</t>
+          <t>Maruti Suzuki India Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5203,12 +5236,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Marico Ltd.</t>
+          <t>Nestle India Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5223,17 +5256,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd.</t>
+          <t>NTPC Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -5243,17 +5276,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MRF Ltd.</t>
+          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5263,17 +5296,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nestle India Ltd.</t>
+          <t>Page Industries Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -5283,17 +5316,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTPC Ltd.</t>
+          <t>Pidilite Industries Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5336,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Page Industries Ltd.</t>
+          <t>Power Grid Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -5323,17 +5356,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd.</t>
+          <t>Reliance Industries Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5343,17 +5376,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Ltd.</t>
+          <t>SBI Cards and Payment Services Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5363,17 +5396,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Reliance Industries Ltd.</t>
+          <t>SBI Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5383,12 +5416,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SBI Cards and Payment Services Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5403,17 +5436,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd.</t>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5423,17 +5456,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5443,17 +5476,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Ltd.</t>
+          <t>Tata Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5463,17 +5496,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>Tata Power Co. Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -5483,17 +5516,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd.</t>
+          <t>Tech Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5503,17 +5536,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tech Mahindra Ltd.</t>
+          <t>Titan Company Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5523,17 +5556,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Titan Company Ltd.</t>
+          <t>Torrent Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5543,17 +5576,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Ltd.</t>
+          <t>UltraTech Cement Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -5563,17 +5596,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>UltraTech Cement Ltd.</t>
+          <t>United Spirits Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5583,17 +5616,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>United Spirits Ltd.</t>
+          <t>Wipro Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5603,17 +5636,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wipro Ltd.</t>
+          <t>Zydus Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -571,7 +571,7 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23213.75</v>
+        <v>23088.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>24.67</v>
+        <v>22.62</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.03787878787878788</v>
+        <v>0.01492537313432836</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>940.9708147547628</v>
+        <v>1020.725022104332</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2616826522583751</v>
+        <v>0.3393344904033586</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04053506282934739</v>
+        <v>0.04420866489832007</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>96.21212121212122</v>
+        <v>98.50746268656717</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>97.34848484848484</v>
+        <v>98.95522388059702</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.27571428571429</v>
+        <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>26606.62190920146</v>
+        <v>28762.57294429708</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.146157855116104</v>
+        <v>0.2457370215990906</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>33.64428571428572</v>
+        <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31658.29094041346</v>
+        <v>34267.19717064544</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3637732352770862</v>
+        <v>0.4841480358721737</v>
       </c>
     </row>
     <row r="16">
@@ -818,7 +818,7 @@
         <v>0.218855498309952</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>0.1463701118425471</v>
+        <v>0.1381146298021416</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0.1825776644607492</v>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="30" t="n">
         <v>0.1243344997343012</v>
@@ -846,7 +846,7 @@
         <v>0.15245932820649</v>
       </c>
       <c r="E19" s="30" t="n">
-        <v>0.1785081032571778</v>
+        <v>0.1747354961145331</v>
       </c>
       <c r="F19" s="30" t="n">
         <v>0.1171198842073442</v>
@@ -862,20 +862,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.111652889184817</v>
+        <v>0.1411397397932215</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0.1419265398225793</v>
+        <v>0.1369676604627205</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>0.1463009130875816</v>
-      </c>
-      <c r="F20" s="30" t="n"/>
+        <v>0.151923783737317</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0.1074548484457203</v>
+      </c>
       <c r="G20" s="30" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="21">
@@ -885,16 +887,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>0.07269742099130849</v>
+        <v>0.07157548525694779</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>0.1711200220152822</v>
+        <v>0.1658256391749801</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>0.1182425537751224</v>
+        <v>0.1118915000689473</v>
       </c>
       <c r="F21" s="30" t="n">
         <v>0.1313046060711542</v>
@@ -913,7 +915,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="30" t="n">
-        <v>0.05080328048427174</v>
+        <v>0.02279280514565701</v>
       </c>
       <c r="D22" s="30" t="n">
         <v>0.1273194898895045</v>
@@ -940,7 +942,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -950,7 +952,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
@@ -973,7 +975,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2292,6 +2294,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>23088.8</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2308,7 +2329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2408,7 +2429,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,C2)+1)/2)/COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2453,7 +2474,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,C3)+1)/2)/COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2498,7 +2519,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,C4)+1)/2)/COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2543,7 +2564,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,C5)+1)/2)/COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2562,7 +2583,10 @@
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="30" t="n"/>
+      <c r="L5" s="30">
+        <f>IFERROR((B45/B5)^(1/10)-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="n">
@@ -2588,7 +2612,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,C6)+1)/2)/COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2633,7 +2657,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,C7)+1)/2)/COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2678,7 +2702,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,C8)+1)/2)/COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2723,7 +2747,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,C9)+1)/2)/COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2768,7 +2792,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,C10)+1)/2)/COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2813,7 +2837,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,C11)+1)/2)/COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2858,7 +2882,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,C12)+1)/2)/COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2903,7 +2927,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,C13)+1)/2)/COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2948,7 +2972,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,C14)+1)/2)/COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2993,7 +3017,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,C15)+1)/2)/COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3038,7 +3062,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,C16)+1)/2)/COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3083,7 +3107,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,C17)+1)/2)/COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3128,7 +3152,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,C18)+1)/2)/COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3173,7 +3197,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,C19)+1)/2)/COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3218,7 +3242,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,C20)+1)/2)/COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3263,7 +3287,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,C21)+1)/2)/COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3308,7 +3332,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,C22)+1)/2)/COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3353,7 +3377,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,C23)+1)/2)/COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3398,7 +3422,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,C24)+1)/2)/COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3443,7 +3467,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,C25)+1)/2)/COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3458,7 +3482,10 @@
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="30" t="n"/>
+      <c r="K25" s="30">
+        <f>IFERROR((B45/B25)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
@@ -3485,7 +3512,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,C26)+1)/2)/COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3527,7 +3554,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,C27)+1)/2)/COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3569,7 +3596,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,C28)+1)/2)/COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3611,7 +3638,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,C29)+1)/2)/COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3653,7 +3680,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,C30)+1)/2)/COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3695,7 +3722,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,C31)+1)/2)/COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3737,7 +3764,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,C32)+1)/2)/COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3779,7 +3806,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,C33)+1)/2)/COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3790,7 +3817,10 @@
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="30" t="n"/>
+      <c r="J33" s="30">
+        <f>IFERROR((B45/B33)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K33" s="30" t="n"/>
       <c r="L33" s="30" t="n"/>
     </row>
@@ -3818,7 +3848,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,C34)+1)/2)/COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3857,7 +3887,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,C35)+1)/2)/COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3896,7 +3926,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,C36)+1)/2)/COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3935,7 +3965,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,C37)+1)/2)/COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -3974,7 +4004,7 @@
         <v/>
       </c>
       <c r="G38" s="30">
-        <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,C38)+1)/2)/COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H38">
@@ -4013,7 +4043,7 @@
         <v/>
       </c>
       <c r="G39" s="30">
-        <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C39="","",(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,C39)+1)/2)/COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H39">
@@ -4052,7 +4082,7 @@
         <v/>
       </c>
       <c r="G40" s="30">
-        <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C40="","",(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,C40)+1)/2)/COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H40">
@@ -4091,14 +4121,17 @@
         <v/>
       </c>
       <c r="G41" s="30">
-        <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C41="","",(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,C41)+1)/2)/COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H41">
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="30" t="n"/>
+      <c r="I41" s="30">
+        <f>IFERROR(B45/B41-1,"")</f>
+        <v/>
+      </c>
       <c r="J41" s="30" t="n"/>
       <c r="K41" s="30" t="n"/>
       <c r="L41" s="30" t="n"/>
@@ -4127,7 +4160,7 @@
         <v/>
       </c>
       <c r="G42" s="30">
-        <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C42="","",(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,C42)+1)/2)/COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H42">
@@ -4163,7 +4196,7 @@
         <v/>
       </c>
       <c r="G43" s="30">
-        <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C43="","",(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,C43)+1)/2)/COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H43">
@@ -4199,7 +4232,7 @@
         <v/>
       </c>
       <c r="G44" s="30">
-        <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C44="","",(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,C44)+1)/2)/COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H44">
@@ -4210,6 +4243,42 @@
       <c r="J44" s="30" t="n"/>
       <c r="K44" s="30" t="n"/>
       <c r="L44" s="30" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B45" s="24" t="n">
+        <v>23088.8</v>
+      </c>
+      <c r="C45" s="25" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E45" s="33">
+        <f>IFERROR(B45/C45,"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="30">
+        <f>IF(AND(D45=D41,E41&lt;&gt;""),E45/E41-1,"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="30">
+        <f>IF(C45="","",(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,C45)+1)/2)/COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H45">
+        <f>IF(G45="","",IF(G45&lt;=20%,"Q1 Cheapest",IF(G45&lt;=40%,"Q2",IF(G45&lt;=60%,"Q3",IF(G45&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I45" s="30" t="n"/>
+      <c r="J45" s="30" t="n"/>
+      <c r="K45" s="30" t="n"/>
+      <c r="L45" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4224,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4232,7 +4301,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4546,6 +4615,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>23088.8</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.0149253731343</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.339334490403</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4586,7 +4688,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23088.8</v>
+        <v>22880.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.62</v>
+        <v>22.41</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.01492537313432836</v>
+        <v>0.007462686567164179</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1020.725022104332</v>
+        <v>1021.001784917448</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3393344904033586</v>
+        <v>0.3395746726524267</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04420866489832007</v>
+        <v>0.04462293618920125</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>98.50746268656717</v>
+        <v>99.25373134328358</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>98.95522388059702</v>
+        <v>99.4776119402985</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28762.57294429708</v>
+        <v>28770.37172499522</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2457370215990906</v>
+        <v>0.2574105947599923</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34267.19717064544</v>
+        <v>34276.48849365717</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4841480358721737</v>
+        <v>0.4980557149231848</v>
       </c>
     </row>
     <row r="16">
@@ -4293,13 +4293,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -4648,6 +4648,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>22880.65</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.339574672652</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4688,7 +4721,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22880.65</v>
+        <v>22947.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.41</v>
+        <v>22.48</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1021.001784917448</v>
+        <v>1020.77846975089</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3395746726524267</v>
+        <v>0.3391499823422346</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04462293618920125</v>
+        <v>0.04448398576512456</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28770.37172499522</v>
+        <v>28764.07902262328</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2574105947599923</v>
+        <v>0.2534951703101169</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34276.48849365717</v>
+        <v>34268.99148449415</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4980557149231848</v>
+        <v>0.4933909506863243</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4681,6 +4681,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>22947.1</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.339149982342</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4721,7 +4754,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22947.1</v>
+        <v>23147.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.48</v>
+        <v>22.67</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.007462686567164179</v>
+        <v>0.02238805970149254</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1020.77846975089</v>
+        <v>1021.052051168946</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3391499823422346</v>
+        <v>0.3397980147677522</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04448398576512456</v>
+        <v>0.04411116012351125</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>99.25373134328358</v>
+        <v>97.76119402985076</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>99.4776119402985</v>
+        <v>98.43283582089552</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28764.07902262328</v>
+        <v>28771.7881561535</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2534951703101169</v>
+        <v>0.2429894763375133</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34268.99148449415</v>
+        <v>34278.17600352889</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4933909506863243</v>
+        <v>0.480874661289306</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4714,6 +4714,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>23147.25</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.339798014768</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4754,7 +4787,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23147.25</v>
+        <v>22947.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.67</v>
+        <v>22.48</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.02238805970149254</v>
+        <v>0.007462686567164179</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1021.052051168946</v>
+        <v>1020.789590747331</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3397980147677522</v>
+        <v>0.3394536210109089</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04411116012351125</v>
+        <v>0.04448398576512456</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>97.76119402985076</v>
+        <v>99.25373134328358</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>98.43283582089552</v>
+        <v>99.4776119402985</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28771.7881561535</v>
+        <v>28764.39239641586</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2429894763375133</v>
+        <v>0.2534951703101167</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34278.17600352889</v>
+        <v>34269.36483223182</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.480874661289306</v>
+        <v>0.4933909506863241</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4747,6 +4747,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>22947.35</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.339453621011</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4787,7 +4820,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22947.35</v>
+        <v>22545.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.48</v>
+        <v>22.08</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1020.789590747331</v>
+        <v>1021.080163043478</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3394536210109089</v>
+        <v>0.3397159803070842</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04448398576512456</v>
+        <v>0.04528985507246377</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28764.39239641586</v>
+        <v>28772.58030861801</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2534951703101167</v>
+        <v>0.2762034161490683</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34269.36483223182</v>
+        <v>34279.11975931677</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4933909506863241</v>
+        <v>0.5204451345755694</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4780,6 +4780,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>22545.45</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.339715980307</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4820,7 +4853,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22545.45</v>
+        <v>22846.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.08</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1021.080163043478</v>
+        <v>1020.862377122431</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3397159803070842</v>
+        <v>0.339574816154953</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04528985507246377</v>
+        <v>0.04468275245755138</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28772.58030861801</v>
+        <v>28766.44341248564</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2762034161490683</v>
+        <v>0.2590961317502871</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34279.11975931677</v>
+        <v>34271.80837482446</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5204451345755694</v>
+        <v>0.5000638325035107</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4813,6 +4813,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>22846.9</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.339574816155</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4853,7 +4886,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22846.9</v>
+        <v>22720.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.38</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1020.862377122431</v>
+        <v>1021.616456834532</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.339574816154953</v>
+        <v>0.3403217233654157</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04468275245755138</v>
+        <v>0.04496402877697842</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28766.44341248564</v>
+        <v>28787.69230151593</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2590961317502871</v>
+        <v>0.2670220966084276</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34271.80837482446</v>
+        <v>34297.12390801645</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5000638325035107</v>
+        <v>0.5095066803699897</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4846,6 +4846,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>22720.75</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.340321723365</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4886,7 +4919,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22720.75</v>
+        <v>23020.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.24</v>
+        <v>22.51</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1021.616456834532</v>
+        <v>1022.67658818303</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3403217233654157</v>
+        <v>0.341651072099628</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04496402877697842</v>
+        <v>0.0444247001332741</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28787.69230151593</v>
+        <v>28817.56528844323</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2670220966084276</v>
+        <v>0.2518245858983308</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34297.12390801645</v>
+        <v>34332.71403185885</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5095066803699897</v>
+        <v>0.4914006473313444</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4879,6 +4879,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>23020.45</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>22.51</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.3416510721</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4919,7 +4952,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23020.45</v>
+        <v>23029.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.51</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1022.67658818303</v>
+        <v>1022.630994671403</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.341651072099628</v>
+        <v>0.3414867185922386</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0444247001332741</v>
+        <v>0.04440497335701599</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28817.56528844323</v>
+        <v>28816.28052841919</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2518245858983308</v>
+        <v>0.2512687135244862</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34332.71403185885</v>
+        <v>34331.18339253996</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4914006473313444</v>
+        <v>0.4907383912712509</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4912,6 +4912,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>23029.65</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.341486718592</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4952,7 +4985,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23029.65</v>
+        <v>23194.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.52</v>
+        <v>22.66</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.007462686567164179</v>
+        <v>0.02238805970149254</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1022.630994671403</v>
+        <v>1023.587819947043</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3414867185922386</v>
+        <v>0.3431104718438338</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04440497335701599</v>
+        <v>0.0441306266548985</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>99.25373134328358</v>
+        <v>97.76119402985076</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>99.4776119402985</v>
+        <v>98.43283582089552</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28816.28052841919</v>
+        <v>28843.24249779347</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2512687135244862</v>
+        <v>0.2435380153826756</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34331.18339253996</v>
+        <v>34363.30538393645</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4907383912712509</v>
+        <v>0.4815281805573068</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4945,6 +4945,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>23194.5</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.343110471844</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4985,7 +5018,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23194.5</v>
+        <v>23262.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.66</v>
+        <v>22.69</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1023.587819947043</v>
+        <v>1025.222565006611</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3431104718438338</v>
+        <v>0.3496757697126047</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0441306266548985</v>
+        <v>0.04407227853680035</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28843.24249779347</v>
+        <v>28889.30727822199</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2435380153826756</v>
+        <v>0.241893848769124</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34363.30538393645</v>
+        <v>34418.18611093621</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4815281805573068</v>
+        <v>0.4795693508782972</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4978,6 +4978,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>23262.3</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>22.69</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.349675769713</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5018,7 +5051,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23262.3</v>
+        <v>23054.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.69</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.02238805970149254</v>
+        <v>0.007462686567164179</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1025.222565006611</v>
+        <v>1030.136282394996</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3496757697126047</v>
+        <v>0.3559008163717943</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04407227853680035</v>
+        <v>0.04468275245755138</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>97.76119402985076</v>
+        <v>99.25373134328358</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>98.43283582089552</v>
+        <v>99.4776119402985</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28889.30727822199</v>
+        <v>29027.76881463041</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.241893848769124</v>
+        <v>0.2590961317502871</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34418.18611093621</v>
+        <v>34583.14662326056</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4795693508782972</v>
+        <v>0.5000638325035105</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5011,6 +5011,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>23054.45</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.355900816372</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5051,7 +5084,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23054.45</v>
+        <v>22993.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.38</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1030.136282394996</v>
+        <v>1030.183691756272</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3559008163717943</v>
+        <v>0.347743497838841</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04468275245755138</v>
+        <v>0.04480286738351254</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>29027.76881463041</v>
+        <v>29029.10474270353</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2590961317502871</v>
+        <v>0.2624807987711213</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34583.14662326056</v>
+        <v>34584.73822324628</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5000638325035105</v>
+        <v>0.5040962621607781</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5044,6 +5044,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>22993.7</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.347743497839</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5084,7 +5117,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22993.7</v>
+        <v>22903.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.32</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1030.183691756272</v>
+        <v>1030.285650022492</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.347743497838841</v>
+        <v>0.3478768853030847</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04480286738351254</v>
+        <v>0.0449842555105713</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>29029.10474270353</v>
+        <v>29031.97778099094</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2624807987711213</v>
+        <v>0.2675920570657411</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34584.73822324628</v>
+        <v>34588.16110789795</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5040962621607781</v>
+        <v>0.5101857207120364</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5077,6 +5077,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>22903.25</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.347876885303</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5117,7 +5150,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22903.25</v>
+        <v>22739.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.23</v>
+        <v>22.07</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1030.285650022492</v>
+        <v>1030.326234707748</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3478768853030847</v>
+        <v>0.3481211304617093</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0449842555105713</v>
+        <v>0.04531037607612143</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>29031.97778099094</v>
+        <v>29033.12139944332</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2675920570657411</v>
+        <v>0.2767816687164215</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34588.16110789795</v>
+        <v>34589.52359376011</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5101857207120364</v>
+        <v>0.5211340539840765</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5110,6 +5110,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>22739.3</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>22.07</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.348121130462</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5150,7 +5183,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22739.3</v>
+        <v>22864.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.07</v>
+        <v>22.19</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1030.326234707748</v>
+        <v>1030.383055430374</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3481211304617093</v>
+        <v>0.3489770962336181</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04531037607612143</v>
+        <v>0.04506534474988733</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>29033.12139944332</v>
+        <v>29034.72252623447</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2767816687164215</v>
+        <v>0.2698770359878966</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34589.52359376011</v>
+        <v>34591.43114659112</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5211340539840765</v>
+        <v>0.512908002317646</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5143,6 +5143,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>22864.2</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.348977096234</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5183,7 +5216,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22864.2</v>
+        <v>22921</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.19</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1030.383055430374</v>
+        <v>1037.618832050702</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3489770962336181</v>
+        <v>0.3592207484400154</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04506534474988733</v>
+        <v>0.04526935264825713</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>29034.72252623447</v>
+        <v>29238.61637457156</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2698770359878966</v>
+        <v>0.2756256871241027</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34591.43114659112</v>
+        <v>34834.34650455927</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.512908002317646</v>
+        <v>0.519756838905775</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5176,6 +5176,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>22921</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>22.09</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.35922074844</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5216,7 +5249,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22921</v>
+        <v>22873.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.09</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1037.618832050702</v>
+        <v>1037.813067150635</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3592207484400154</v>
+        <v>0.3581066503522945</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04526935264825713</v>
+        <v>0.04537205081669692</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>29238.61637457156</v>
+        <v>29244.08964220897</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2756256871241027</v>
+        <v>0.2785195747990665</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34834.34650455927</v>
+        <v>34840.86725434275</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.519756838905775</v>
+        <v>0.5232045631319677</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5209,6 +5209,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>22873.4</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.358106650352</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5249,7 +5282,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22873.4</v>
+        <v>23125.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.04</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1037.813067150635</v>
+        <v>1037.503364737551</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3581066503522945</v>
+        <v>0.3555492614489859</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04537205081669692</v>
+        <v>0.04486316733961418</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>29244.08964220897</v>
+        <v>29235.36267064026</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2785195747990665</v>
+        <v>0.2641799653912709</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34840.86725434275</v>
+        <v>34830.47010190348</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5232045631319677</v>
+        <v>0.5061206178299047</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5242,6 +5242,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>23125.95</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.355549261449</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5282,7 +5315,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-low-volatility-50.xlsx
+++ b/docs/downloads/indices/nifty-low-volatility-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23125.95</v>
+        <v>23279.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.29</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1037.503364737551</v>
+        <v>1040.172028596962</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.3555492614489859</v>
+        <v>0.3591590945931276</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04486316733961418</v>
+        <v>0.04468275245755138</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>28.17857142857143</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>29235.36267064026</v>
+        <v>29310.56180582152</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2641799653912709</v>
+        <v>0.2590961317502871</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.57142857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>34830.47010190348</v>
+        <v>34920.06096004085</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5061206178299047</v>
+        <v>0.5000638325035107</v>
       </c>
     </row>
     <row r="16">
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5275,6 +5275,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>23279.05</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.359159094593</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5315,7 +5348,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
